--- a/data/trans_dic/P62-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,68</t>
+          <t>0,27; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,3</t>
+          <t>0,32; 3,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,12</t>
+          <t>1,18; 5,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,44</t>
+          <t>1,99; 6,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,21</t>
+          <t>0,67; 6,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,25</t>
+          <t>1,08; 3,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,96</t>
+          <t>1,46; 4,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,7</t>
+          <t>0,33; 3,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,89</t>
+          <t>1,57; 8,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,82</t>
+          <t>3,32; 8,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,73</t>
+          <t>3,0; 9,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 22,72</t>
+          <t>4,57; 23,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,67</t>
+          <t>1,81; 6,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,36</t>
+          <t>5,19; 11,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,85</t>
+          <t>2,6; 7,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 13,18</t>
+          <t>3,95; 12,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,13</t>
+          <t>2,1; 5,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,08</t>
+          <t>4,81; 9,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,4</t>
+          <t>3,57; 7,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 14,01</t>
+          <t>5,4; 14,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,95; 47,74</t>
+          <t>24,84; 49,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 25,11</t>
+          <t>13,48; 24,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 19,41</t>
+          <t>9,88; 19,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 39,03</t>
+          <t>17,49; 38,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,74</t>
+          <t>3,08; 7,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 13,24</t>
+          <t>6,8; 13,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,04</t>
+          <t>6,14; 11,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 18,46</t>
+          <t>10,42; 18,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,06</t>
+          <t>7,23; 12,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,85</t>
+          <t>10,2; 15,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,7</t>
+          <t>8,33; 13,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,02</t>
+          <t>13,62; 22,48</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,35; 68,21</t>
+          <t>45,62; 68,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,0; 37,97</t>
+          <t>25,39; 37,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,06; 34,82</t>
+          <t>23,7; 35,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,49; 48,99</t>
+          <t>31,82; 48,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,5</t>
+          <t>8,99; 15,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 18,8</t>
+          <t>11,16; 18,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 15,79</t>
+          <t>9,06; 15,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 19,92</t>
+          <t>12,56; 19,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 24,75</t>
+          <t>16,84; 24,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 24,11</t>
+          <t>17,75; 24,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,8; 22,04</t>
+          <t>16,05; 22,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 28,9</t>
+          <t>20,47; 28,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,78; 83,24</t>
+          <t>71,28; 83,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,79; 71,08</t>
+          <t>58,98; 71,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,67; 70,15</t>
+          <t>58,83; 69,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,6; 70,45</t>
+          <t>59,82; 70,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,94; 28,82</t>
+          <t>19,65; 28,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,08; 30,74</t>
+          <t>21,23; 30,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,46; 34,72</t>
+          <t>24,67; 34,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,6; 36,02</t>
+          <t>28,08; 35,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41,26; 49,42</t>
+          <t>40,97; 49,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,13; 46,59</t>
+          <t>38,1; 46,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,11; 49,18</t>
+          <t>41,08; 48,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,01; 49,67</t>
+          <t>42,99; 49,82</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96,56; 99,42</t>
+          <t>96,68; 99,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98,15; 100,0</t>
+          <t>98,21; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96,65; 99,42</t>
+          <t>96,44; 99,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,82; 87,97</t>
+          <t>82,0; 88,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,74; 57,08</t>
+          <t>47,32; 57,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,7; 69,9</t>
+          <t>59,29; 69,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,34; 68,32</t>
+          <t>57,98; 68,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,78; 89,55</t>
+          <t>57,79; 88,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,22; 76,96</t>
+          <t>70,12; 77,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77,86; 84,04</t>
+          <t>77,94; 84,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76,25; 83,0</t>
+          <t>76,71; 82,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70,66; 88,73</t>
+          <t>70,83; 89,25</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97,52; 100,0</t>
+          <t>97,5; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>97,85; 100,0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>97,87; 100,0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>97,76; 100,0</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84,71; 90,93</t>
+          <t>84,41; 90,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,67; 79,1</t>
+          <t>69,34; 78,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,52; 81,04</t>
+          <t>72,4; 81,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,31; 79,29</t>
+          <t>68,86; 79,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,54; 78,31</t>
+          <t>72,3; 78,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,81; 87,08</t>
+          <t>80,5; 87,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82,69; 88,26</t>
+          <t>82,5; 88,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80,45; 87,07</t>
+          <t>80,91; 87,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,18; 82,6</t>
+          <t>78,11; 82,49</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>51,84; 57,23</t>
+          <t>51,94; 57,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,5; 46,28</t>
+          <t>41,76; 46,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,11; 48,56</t>
+          <t>44,08; 48,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,19; 57,15</t>
+          <t>51,16; 57,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,8; 26,4</t>
+          <t>22,96; 26,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,18; 30,79</t>
+          <t>27,43; 30,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,31; 32,25</t>
+          <t>28,23; 32,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,79; 62,01</t>
+          <t>36,89; 59,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,06; 37,23</t>
+          <t>34,13; 37,28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,16; 37,13</t>
+          <t>34,15; 36,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,94; 38,83</t>
+          <t>35,76; 38,64</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,09; 59,01</t>
+          <t>44,13; 58,3</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4715</t>
+          <t>0; 5000</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>976; 9643</t>
+          <t>977; 9472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1399; 10786</t>
+          <t>1062; 10471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 12079</t>
+          <t>0; 9516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4645; 17449</t>
+          <t>4026; 18097</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5744; 18611</t>
+          <t>5750; 18851</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1499; 14056</t>
+          <t>1523; 14165</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7626</t>
+          <t>0; 6667</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6965; 22756</t>
+          <t>7597; 23368</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8642; 24379</t>
+          <t>8985; 24603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2327; 19778</t>
+          <t>1756; 18130</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2668; 13751</t>
+          <t>2737; 13934</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9881; 26484</t>
+          <t>9972; 26230</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8325; 23678</t>
+          <t>7313; 22039</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3285; 16321</t>
+          <t>3284; 16762</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5327; 18957</t>
+          <t>5154; 18854</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16705; 37253</t>
+          <t>17036; 37234</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7112; 22331</t>
+          <t>7402; 21449</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6255; 20907</t>
+          <t>6264; 20252</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9654; 28071</t>
+          <t>9615; 27006</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30493; 57063</t>
+          <t>30229; 56531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18937; 39085</t>
+          <t>18853; 39740</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12507; 32278</t>
+          <t>12444; 32677</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16689; 33261</t>
+          <t>17305; 34481</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34895; 63151</t>
+          <t>33887; 61834</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19654; 40405</t>
+          <t>20564; 39908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12339; 28134</t>
+          <t>12607; 27740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12297; 29752</t>
+          <t>11836; 30304</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28457; 55110</t>
+          <t>28330; 54831</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21442; 41305</t>
+          <t>21070; 40732</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19421; 35021</t>
+          <t>19764; 35377</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33097; 59281</t>
+          <t>32827; 58367</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70423; 105840</t>
+          <t>68134; 103710</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46863; 75539</t>
+          <t>45911; 74491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36048; 57639</t>
+          <t>35660; 58835</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36655; 55133</t>
+          <t>36870; 55531</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61221; 92975</t>
+          <t>62173; 92024</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63895; 96483</t>
+          <t>65665; 97461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42748; 66501</t>
+          <t>43199; 66067</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29563; 53441</t>
+          <t>30989; 54863</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41398; 71904</t>
+          <t>42696; 70641</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36050; 62199</t>
+          <t>35695; 61799</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32775; 51187</t>
+          <t>32274; 51085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70383; 105306</t>
+          <t>71668; 105880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>109333; 151249</t>
+          <t>111361; 154183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>106006; 147900</t>
+          <t>107696; 148870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82110; 113478</t>
+          <t>80394; 112191</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>158358; 183640</t>
+          <t>157243; 183226</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>157565; 190480</t>
+          <t>158066; 192065</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182054; 217670</t>
+          <t>182557; 216617</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155408; 183716</t>
+          <t>155990; 183832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>67552; 97650</t>
+          <t>66580; 97352</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78202; 114061</t>
+          <t>78765; 114787</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93747; 133099</t>
+          <t>94548; 132172</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95537; 120348</t>
+          <t>93792; 119034</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>230814; 276501</t>
+          <t>229211; 275537</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>243664; 297715</t>
+          <t>243485; 295564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>285111; 341087</t>
+          <t>284968; 339823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>255838; 295432</t>
+          <t>255729; 296351</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>280030; 288345</t>
+          <t>280374; 288356</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>301107; 306770</t>
+          <t>301275; 306770</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>317208; 326296</t>
+          <t>316521; 326271</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>287367; 308985</t>
+          <t>288007; 309281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>158212; 193195</t>
+          <t>160147; 193444</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>207912; 243423</t>
+          <t>206457; 242556</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>215024; 251807</t>
+          <t>213709; 252419</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>340290; 527377</t>
+          <t>340293; 523028</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>441335; 483667</t>
+          <t>440718; 485195</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>510005; 550463</t>
+          <t>510536; 551072</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>531299; 578362</t>
+          <t>534544; 578188</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>664273; 834134</t>
+          <t>665922; 839032</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>202260; 207412</t>
+          <t>202221; 207412</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>244528; 249851</t>
+          <t>244491; 249851</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>246452; 252094</t>
+          <t>246712; 252094</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>238161; 255654</t>
+          <t>237326; 254840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>228556; 263261</t>
+          <t>230802; 262729</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>280565; 313548</t>
+          <t>280107; 313613</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>274597; 314140</t>
+          <t>272817; 313101</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>307203; 331649</t>
+          <t>306211; 331261</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>436588; 470422</t>
+          <t>434887; 470160</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>526506; 561995</t>
+          <t>525309; 562931</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>521564; 564487</t>
+          <t>524541; 566298</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>550930; 582094</t>
+          <t>550407; 581291</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>704703; 777999</t>
+          <t>706023; 776905</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>822352; 917084</t>
+          <t>827419; 915256</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>858465; 945068</t>
+          <t>857980; 945922</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>757945; 846187</t>
+          <t>757511; 850378</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>535011; 619576</t>
+          <t>538793; 620420</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>699546; 792414</t>
+          <t>705813; 795939</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>695881; 792794</t>
+          <t>693930; 788550</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>801281; 1350692</t>
+          <t>803430; 1297233</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1262052; 1379693</t>
+          <t>1264825; 1381379</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1556186; 1691213</t>
+          <t>1555651; 1682935</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1583199; 1710332</t>
+          <t>1575264; 1701824</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1612998; 2158940</t>
+          <t>1614534; 2133061</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -717,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,63</t>
+          <t>0,27; 2,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,2</t>
+          <t>0,32; 3,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,31</t>
+          <t>1,37; 5,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,53</t>
+          <t>2,0; 6,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,26</t>
+          <t>0,55; 6,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,34</t>
+          <t>1,01; 3,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,0</t>
+          <t>1,44; 3,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,39</t>
+          <t>0,31; 3,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,0</t>
+          <t>1,34; 7,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,73</t>
+          <t>3,3; 8,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,05</t>
+          <t>3,45; 9,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 23,33</t>
+          <t>4,62; 20,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,64</t>
+          <t>1,73; 6,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,35</t>
+          <t>5,02; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,54</t>
+          <t>2,36; 7,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,77</t>
+          <t>3,71; 12,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,89</t>
+          <t>2,28; 5,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,0</t>
+          <t>4,82; 8,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,53</t>
+          <t>3,41; 7,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 14,18</t>
+          <t>5,18; 12,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,84; 49,49</t>
+          <t>25,95; 48,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,48; 24,59</t>
+          <t>13,3; 24,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 19,17</t>
+          <t>9,93; 19,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 38,49</t>
+          <t>16,89; 37,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,88</t>
+          <t>3,2; 7,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,17</t>
+          <t>6,72; 13,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,87</t>
+          <t>6,19; 12,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,42; 18,65</t>
+          <t>9,41; 17,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,85</t>
+          <t>7,12; 12,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 15,53</t>
+          <t>10,13; 15,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,51</t>
+          <t>8,17; 13,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 22,48</t>
+          <t>12,74; 20,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,62; 68,7</t>
+          <t>44,74; 67,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,39; 37,58</t>
+          <t>25,49; 37,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,7; 35,18</t>
+          <t>23,29; 34,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,82; 48,67</t>
+          <t>32,1; 49,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 15,91</t>
+          <t>8,7; 15,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 18,47</t>
+          <t>10,91; 18,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 15,69</t>
+          <t>9,33; 15,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,88</t>
+          <t>13,25; 20,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 24,88</t>
+          <t>16,67; 24,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 24,58</t>
+          <t>17,47; 24,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 22,19</t>
+          <t>16,06; 22,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 28,57</t>
+          <t>21,21; 29,12</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,28; 83,05</t>
+          <t>71,69; 83,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,98; 71,67</t>
+          <t>59,04; 71,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,83; 69,81</t>
+          <t>59,0; 69,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,82; 70,5</t>
+          <t>58,8; 69,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,65; 28,73</t>
+          <t>19,52; 28,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,23; 30,94</t>
+          <t>21,2; 30,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 34,48</t>
+          <t>24,69; 34,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,08; 35,63</t>
+          <t>28,41; 36,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,97; 49,25</t>
+          <t>41,03; 49,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,1; 46,25</t>
+          <t>38,11; 46,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,08; 48,99</t>
+          <t>41,3; 48,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,99; 49,82</t>
+          <t>42,44; 49,07</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96,68; 99,43</t>
+          <t>96,64; 99,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98,21; 100,0</t>
+          <t>98,16; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96,44; 99,41</t>
+          <t>96,71; 99,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,0; 88,06</t>
+          <t>82,36; 88,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,32; 57,15</t>
+          <t>47,08; 57,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,29; 69,65</t>
+          <t>59,65; 69,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,98; 68,48</t>
+          <t>58,1; 68,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,79; 88,82</t>
+          <t>56,26; 63,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,12; 77,2</t>
+          <t>70,41; 77,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77,94; 84,13</t>
+          <t>77,78; 84,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76,71; 82,98</t>
+          <t>76,77; 82,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70,83; 89,25</t>
+          <t>69,77; 74,7</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97,5; 100,0</t>
+          <t>97,12; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97,85; 100,0</t>
+          <t>98,05; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,87; 100,0</t>
+          <t>97,57; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84,41; 90,64</t>
+          <t>84,97; 90,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,34; 78,94</t>
+          <t>68,74; 79,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,4; 81,06</t>
+          <t>72,42; 81,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,86; 79,02</t>
+          <t>69,52; 79,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,3; 78,22</t>
+          <t>72,73; 78,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,5; 87,03</t>
+          <t>80,19; 87,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82,5; 88,41</t>
+          <t>82,81; 88,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80,91; 87,35</t>
+          <t>80,7; 87,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,11; 82,49</t>
+          <t>78,56; 82,73</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>51,94; 57,15</t>
+          <t>51,86; 57,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,76; 46,19</t>
+          <t>41,74; 46,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,08; 48,6</t>
+          <t>43,94; 48,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,16; 57,44</t>
+          <t>52,16; 57,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,96; 26,44</t>
+          <t>22,86; 26,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,93</t>
+          <t>27,22; 30,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,08</t>
+          <t>28,2; 32,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,89; 59,56</t>
+          <t>35,12; 38,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,13; 37,28</t>
+          <t>34,19; 37,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,15; 36,95</t>
+          <t>34,19; 37,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,76; 38,64</t>
+          <t>35,92; 38,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,13; 58,3</t>
+          <t>42,86; 46,05</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7138</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5000</t>
+          <t>0; 6337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>977; 9472</t>
+          <t>973; 9663</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1062; 10471</t>
+          <t>1061; 11232</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 9516</t>
+          <t>0; 8826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4980</t>
+          <t>0; 5920</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4026; 18097</t>
+          <t>4667; 17919</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5750; 18851</t>
+          <t>5789; 19161</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1523; 14165</t>
+          <t>1469; 16043</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6667</t>
+          <t>0; 6625</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7597; 23368</t>
+          <t>7058; 22657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8985; 24603</t>
+          <t>8856; 24538</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1756; 18130</t>
+          <t>1740; 18752</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>21508</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2737; 13934</t>
+          <t>2341; 12476</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9972; 26230</t>
+          <t>9899; 25373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7313; 22039</t>
+          <t>8394; 23934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3284; 16762</t>
+          <t>3683; 16661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5154; 18854</t>
+          <t>4905; 19734</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17036; 37234</t>
+          <t>16471; 36742</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7402; 21449</t>
+          <t>6719; 20237</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6264; 20252</t>
+          <t>6744; 22662</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9615; 27006</t>
+          <t>10437; 27341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30229; 56531</t>
+          <t>30289; 56076</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18853; 39740</t>
+          <t>17977; 39846</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12444; 32677</t>
+          <t>13555; 33955</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46463</t>
+          <t>49578</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17305; 34481</t>
+          <t>18082; 33693</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33887; 61834</t>
+          <t>33452; 60757</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20564; 39908</t>
+          <t>20667; 40515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12607; 27740</t>
+          <t>13543; 30462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11836; 30304</t>
+          <t>12294; 29971</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28330; 54831</t>
+          <t>27977; 54108</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21070; 40732</t>
+          <t>21251; 41484</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19764; 35377</t>
+          <t>20983; 38069</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32827; 58367</t>
+          <t>32333; 58937</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68134; 103710</t>
+          <t>67640; 106044</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45911; 74491</t>
+          <t>45014; 74430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35660; 58835</t>
+          <t>38615; 62246</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>46132</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95907</t>
+          <t>106848</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36870; 55531</t>
+          <t>36164; 54551</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62173; 92024</t>
+          <t>62417; 91821</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65665; 97461</t>
+          <t>64512; 95682</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43199; 66067</t>
+          <t>48215; 74039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30989; 54863</t>
+          <t>29978; 53561</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42696; 70641</t>
+          <t>41724; 70396</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35695; 61799</t>
+          <t>36759; 62684</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32274; 51085</t>
+          <t>36952; 57097</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71668; 105880</t>
+          <t>70939; 103132</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111361; 154183</t>
+          <t>109578; 153936</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107696; 148870</t>
+          <t>107781; 149894</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80394; 112191</t>
+          <t>91010; 124957</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170209</t>
+          <t>179528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>106361</t>
+          <t>117879</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>276570</t>
+          <t>297408</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>157243; 183226</t>
+          <t>158155; 183199</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>158066; 192065</t>
+          <t>158224; 191008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182557; 216617</t>
+          <t>183083; 217065</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155990; 183832</t>
+          <t>163647; 194090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66580; 97352</t>
+          <t>66155; 97199</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78765; 114787</t>
+          <t>78662; 113602</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94548; 132172</t>
+          <t>94653; 132718</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93792; 119034</t>
+          <t>105499; 135273</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>229211; 275537</t>
+          <t>229545; 276127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>243485; 295564</t>
+          <t>243541; 297642</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>284968; 339823</t>
+          <t>286447; 339363</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>255729; 296351</t>
+          <t>275677; 318797</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299517</t>
+          <t>331580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>431816</t>
+          <t>249490</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>731333</t>
+          <t>581071</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>280374; 288356</t>
+          <t>280260; 288335</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>301275; 306770</t>
+          <t>301119; 306770</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316521; 326271</t>
+          <t>317404; 326293</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>288007; 309281</t>
+          <t>319495; 341891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>160147; 193444</t>
+          <t>159336; 193912</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>206457; 242556</t>
+          <t>207708; 242909</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>213709; 252419</t>
+          <t>214145; 252318</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>340293; 523028</t>
+          <t>234875; 263979</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>440718; 485195</t>
+          <t>442538; 484120</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>510536; 551072</t>
+          <t>509435; 550793</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>534544; 578188</t>
+          <t>534954; 577084</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>665922; 839032</t>
+          <t>561932; 601679</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247165</t>
+          <t>271675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>319332</t>
+          <t>349990</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>566497</t>
+          <t>621665</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>202221; 207412</t>
+          <t>201436; 207412</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>244491; 249851</t>
+          <t>244977; 249851</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>246712; 252094</t>
+          <t>245963; 252094</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237326; 254840</t>
+          <t>262018; 280009</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>230802; 262729</t>
+          <t>228789; 263211</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>280107; 313613</t>
+          <t>280202; 314692</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>272817; 313101</t>
+          <t>275446; 313860</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>306211; 331261</t>
+          <t>336130; 361871</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>434887; 470160</t>
+          <t>433249; 469995</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>525309; 562931</t>
+          <t>527271; 562333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>524541; 566298</t>
+          <t>523174; 564591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>550407; 581291</t>
+          <t>605355; 637501</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>801470</t>
+          <t>874450</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>942962</t>
+          <t>810764</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1744432</t>
+          <t>1685213</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>706023; 776905</t>
+          <t>704978; 776480</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>827419; 915256</t>
+          <t>827071; 916749</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>857980; 945922</t>
+          <t>855290; 942040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>757511; 850378</t>
+          <t>827195; 916420</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>538793; 620420</t>
+          <t>536304; 621544</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>705813; 795939</t>
+          <t>700539; 796120</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>693930; 788550</t>
+          <t>693138; 788114</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>803430; 1297233</t>
+          <t>772622; 847928</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1264825; 1381379</t>
+          <t>1267016; 1382544</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1555651; 1682935</t>
+          <t>1557149; 1690707</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1575264; 1701824</t>
+          <t>1582330; 1705488</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1614534; 2133061</t>
+          <t>1622520; 1743348</t>
         </is>
       </c>
     </row>
